--- a/Ficheiros EXCEL/Entregas_Teste_100.xlsx
+++ b/Ficheiros EXCEL/Entregas_Teste_100.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:P101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,25 +451,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>Peso_KG</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Volume_m3</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Prioridade</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Janela_Inicio</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Janela_Fim</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Janela2_Inicio</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Janela2_Fim</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Janela3_Inicio</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Janela3_Fim</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Observacoes</t>
         </is>
@@ -483,40 +518,57 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5 de Outubro</t>
+          <t>Cabeço da Fonte</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1050-615</t>
+          <t>2640-373</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>190.7</v>
+        <v>39.0457804</v>
       </c>
       <c r="F2" t="n">
+        <v>-9.400972400000001</v>
+      </c>
+      <c r="G2" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,36 +578,57 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Rua da Nau Catrineta</t>
+          <t>Casal Velho</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1990-947</t>
+          <t>2550-481</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cadaval                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>165.8</v>
+        <v>39.2129283</v>
       </c>
       <c r="F3" t="n">
+        <v>-9.072021700000001</v>
+      </c>
+      <c r="G3" t="n">
+        <v>174.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="I3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -565,40 +638,57 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Rua Luís Cristino da Silva, Bairro dos Lóios, Marvila, Lisboa, 1950-172, Portugal</t>
+          <t>Grilo A-dos-Loucos</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1950-891</t>
+          <t>2600-203</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Vila Franca de Xira                                                                                                                                                                                                                                            </t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>188.2</v>
+        <v>38.9392987</v>
       </c>
       <c r="F4" t="n">
+        <v>-9.0182591</v>
+      </c>
+      <c r="G4" t="n">
+        <v>33.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I4" t="n">
         <v>2</v>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -608,12 +698,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Benfica</t>
+          <t>Doutor Estêvão de Vasconcelos</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1500-985</t>
+          <t>1950-602</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -622,26 +712,43 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>79.8</v>
+        <v>38.7457018</v>
       </c>
       <c r="F5" t="n">
+        <v>-9.1014924</v>
+      </c>
+      <c r="G5" t="n">
+        <v>148.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="I5" t="n">
         <v>2</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -651,36 +758,57 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Largo Doutor António Viana</t>
+          <t>Campolide</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1250-855</t>
+          <t>1099-678</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Lisboa</t>
+          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>72.8</v>
+        <v>38.7338599</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
+        <v>-9.160125900000001</v>
+      </c>
+      <c r="G6" t="n">
+        <v>117.4</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -690,36 +818,53 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calhariz de Benfica</t>
+          <t>Parque Gozundeira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1500-262</t>
+          <t>2590-579</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
+          <t xml:space="preserve">Sobral de Monte Agraço                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Fragil</t>
         </is>
@@ -733,40 +878,57 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Adelaide Cabete</t>
+          <t>Gomes Leal</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1500-814</t>
+          <t>2790-624</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>187.1</v>
+        <v>38.7272938</v>
       </c>
       <c r="F8" t="n">
+        <v>-9.2410178</v>
+      </c>
+      <c r="G8" t="n">
+        <v>155</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I8" t="n">
         <v>2</v>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -776,40 +938,57 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Doutor Eduardo Neves</t>
+          <t>Moinho</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1050-263</t>
+          <t>2715-265</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>130.3</v>
+        <v>38.8573958</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+        <v>-9.3249187</v>
+      </c>
+      <c r="G9" t="n">
+        <v>55.6</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -819,12 +998,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Corsário das Ilhas</t>
+          <t>Filipe Folque</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1990-975</t>
+          <t>1050-131</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -833,22 +1012,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>167.9</v>
+        <v>38.7328296</v>
       </c>
       <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="inlineStr">
+        <v>-9.1492285</v>
+      </c>
+      <c r="G10" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -858,38 +1058,59 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alberto José Pessoa Bairro dos Alfinetes</t>
+          <t>Cesário Verde Bairro dos Troviscais</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1950-747</t>
+          <t>2695-820</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>46.8</v>
+        <v>38.8303844</v>
       </c>
       <c r="F11" t="n">
+        <v>-9.108132700000001</v>
+      </c>
+      <c r="G11" t="n">
+        <v>28</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="I11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Fragil</t>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Urgente</t>
         </is>
       </c>
     </row>
@@ -901,36 +1122,53 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Alfredo Guisado</t>
+          <t>Combatentes</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1500-348</t>
+          <t>2670-889</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>178.5</v>
-      </c>
-      <c r="F12" t="n">
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>31.8</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="I12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -940,36 +1178,57 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Beirolas</t>
+          <t>Chafariz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1800-193</t>
+          <t>2685-113</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>170</v>
+        <v>38.7928909</v>
       </c>
       <c r="F13" t="n">
-        <v>1</v>
-      </c>
-      <c r="G13" t="inlineStr">
+        <v>-9.107356100000001</v>
+      </c>
+      <c r="G13" t="n">
+        <v>118.6</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -979,12 +1238,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Cerejais</t>
+          <t>Tapada</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>1600-829</t>
+          <t>1300-254</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -992,23 +1251,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>152.7</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="n">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="I14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1018,36 +1294,57 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Sequeira</t>
+          <t>Poços</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1100-432</t>
+          <t>2580-181</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Alenquer                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>64.90000000000001</v>
+        <v>39.021573</v>
       </c>
       <c r="F15" t="n">
+        <v>-8.9762019</v>
+      </c>
+      <c r="G15" t="n">
+        <v>94</v>
+      </c>
+      <c r="H15" t="n">
         <v>2</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>1</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1057,12 +1354,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Carlos Paredes Alta de Lisboa</t>
+          <t>Conde Almoster</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1750-625</t>
+          <t>1500-591</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1070,23 +1367,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E16" t="n">
-        <v>23.6</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="n">
+        <v>118.1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I16" t="n">
         <v>3</v>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1096,36 +1410,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>François Mitterrand Bairro Armador</t>
+          <t>Doutor Joaquim Namorado</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1950-805</t>
+          <t>2700-258</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Amadora                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>86.59999999999999</v>
+        <v>38.7661883</v>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+        <v>-9.229581899999999</v>
+      </c>
+      <c r="G17" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1135,36 +1474,57 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Belém</t>
+          <t>Carrasqueira</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1300-924</t>
+          <t>2630-434</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Arruda dos Vinhos                                                                                                                                                                                                                                              </t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>41</v>
+        <v>38.9882742</v>
       </c>
       <c r="F18" t="n">
+        <v>-9.082561699999999</v>
+      </c>
+      <c r="G18" t="n">
+        <v>70</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="I18" t="n">
         <v>1</v>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1174,36 +1534,53 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>João Graça Barreto</t>
+          <t>Renolgo</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1950-781</t>
+          <t>2715-933</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>190.6</v>
-      </c>
-      <c r="F19" t="n">
-        <v>3</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="n">
+        <v>102.4</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1213,40 +1590,57 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Forte da Ameixoeira</t>
+          <t>Amarelas Casais das Amarelas</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1750-598</t>
+          <t>2050-662</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Azambuja                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>130.6</v>
+        <v>39.1278994</v>
       </c>
       <c r="F20" t="n">
+        <v>-8.920145</v>
+      </c>
+      <c r="G20" t="n">
+        <v>44.5</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="I20" t="n">
         <v>1</v>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1256,36 +1650,57 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>São Nicolau</t>
+          <t>Bela Vista Bairro Alto de São Lourenço</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1100-643</t>
+          <t>2690-304</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14.2</v>
+        <v>38.8404982</v>
       </c>
       <c r="F21" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" t="inlineStr">
+        <v>-9.1041455</v>
+      </c>
+      <c r="G21" t="n">
+        <v>91.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1295,36 +1710,57 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Jorge Afonso</t>
+          <t>Doutor Carlos Leal</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1600-852</t>
+          <t>2600-404</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Vila Franca de Xira                                                                                                                                                                                                                                            </t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>81</v>
+        <v>38.9885454</v>
       </c>
       <c r="F22" t="n">
+        <v>-8.9696301</v>
+      </c>
+      <c r="G22" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1334,38 +1770,55 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Bica Anjos</t>
+          <t>Alexandre Gomes Mealhada</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1170-256</t>
+          <t>2670-930</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>107.9</v>
-      </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-      <c r="G23" t="inlineStr">
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="n">
+        <v>128.9</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="I23" t="n">
+        <v>2</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -1377,40 +1830,57 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Circunvalação Buraca</t>
+          <t>Beloura Quinta da Beloura</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1500-871</t>
+          <t>2710-661</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>115.1</v>
+        <v>38.7643073</v>
       </c>
       <c r="F24" t="n">
+        <v>-9.374004100000001</v>
+      </c>
+      <c r="G24" t="n">
+        <v>176</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1420,36 +1890,53 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Instituto Bacteriológico</t>
+          <t>Alecrim</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>1150-611</t>
+          <t>2655-941</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>115.1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>64.8</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="I25" t="n">
+        <v>2</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1459,40 +1946,57 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Visconde Valmor</t>
+          <t>São Vicente</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1050-141</t>
+          <t>2530-385</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Lourinhã                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>55.4</v>
+        <v>39.1947228</v>
       </c>
       <c r="F26" t="n">
-        <v>2</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+        <v>-9.268820399999999</v>
+      </c>
+      <c r="G26" t="n">
+        <v>121.4</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1502,12 +2006,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Dom António Caetano de Sousa</t>
+          <t>Santa Apolónia</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1500-772</t>
+          <t>1100-933</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1516,26 +2020,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>136.4</v>
+        <v>38.7172902</v>
       </c>
       <c r="F27" t="n">
-        <v>2</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+        <v>-9.119668300000001</v>
+      </c>
+      <c r="G27" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1545,36 +2066,57 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Infante Dom Henrique</t>
+          <t>Nossa Senhora Anunciação Monte da Vinha</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1800-798</t>
+          <t>2530-247</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Lourinhã                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>135.7</v>
+        <v>39.2497523</v>
       </c>
       <c r="F28" t="n">
+        <v>-9.2896468</v>
+      </c>
+      <c r="G28" t="n">
+        <v>125.8</v>
+      </c>
+      <c r="H28" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
         <v>1</v>
       </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Fragil</t>
         </is>
@@ -1588,12 +2130,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Almada Negreiros</t>
+          <t>Manutenção</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1800-672</t>
+          <t>1900-219</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1601,23 +2143,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E29" t="n">
-        <v>199.4</v>
-      </c>
-      <c r="F29" t="n">
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="n">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="I29" t="n">
         <v>3</v>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1627,38 +2186,59 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Gregório Lopes Torres do Restelo</t>
+          <t>Sem Nome</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1400-839</t>
+          <t>2050-764</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Azambuja                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>98</v>
+        <v>39.1153619</v>
       </c>
       <c r="F30" t="n">
+        <v>-8.885676</v>
+      </c>
+      <c r="G30" t="n">
+        <v>185.1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="I30" t="n">
         <v>2</v>
       </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Urgente</t>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -1670,40 +2250,57 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Conde Valbom</t>
+          <t>Cisterna</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1069-332</t>
+          <t>2580-710</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Alenquer                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>70.5</v>
+        <v>39.1445858</v>
       </c>
       <c r="F31" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" t="inlineStr">
+        <v>-9.019842799999999</v>
+      </c>
+      <c r="G31" t="n">
+        <v>196</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1</v>
+      </c>
+      <c r="J31" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1713,36 +2310,53 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Salvador Correia de Sá</t>
+          <t>Dona Maria I</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1200-193</t>
+          <t>2785-891</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>67.09999999999999</v>
-      </c>
-      <c r="F32" t="n">
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="n">
+        <v>25.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="I32" t="n">
         <v>2</v>
       </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1752,36 +2366,61 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Castelo Picão</t>
+          <t>Quinta do Mor Vale Coelho</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1100-611</t>
+          <t>2050-875</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Azambuja                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>64</v>
+        <v>39.1451933</v>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+        <v>-8.915054700000001</v>
+      </c>
+      <c r="G33" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1791,40 +2430,57 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Frederico George Alto da Faia</t>
+          <t>Alcachofras Lourel</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1600-335</t>
+          <t>2710-367</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>113.5</v>
+        <v>38.8096197</v>
       </c>
       <c r="F34" t="n">
+        <v>-9.370347000000001</v>
+      </c>
+      <c r="G34" t="n">
+        <v>169.3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I34" t="n">
         <v>1</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1834,40 +2490,57 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Professor Reinaldo dos Santos</t>
+          <t>Joaquim Ereira</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1500-418</t>
+          <t>2750-992</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>56.9</v>
+        <v>38.7045715</v>
       </c>
       <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+        <v>-9.4346531</v>
+      </c>
+      <c r="G35" t="n">
+        <v>114.8</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="I35" t="n">
+        <v>3</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1877,36 +2550,53 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rua Abranches Ferrão</t>
+          <t>Bernardo Santareno Alto de Famões</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1600-500</t>
+          <t>1685-958</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Lisboa</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>135.5</v>
-      </c>
-      <c r="F36" t="n">
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H36" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="I36" t="n">
         <v>3</v>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1916,12 +2606,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sul</t>
+          <t>7 Moinhos</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1800-952</t>
+          <t>1350-322</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1930,22 +2620,47 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>135.4</v>
+        <v>38.7221093</v>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+        <v>-9.1691637</v>
+      </c>
+      <c r="G37" t="n">
+        <v>199.3</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1955,36 +2670,61 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>José António Lopes</t>
+          <t>Casal da Amieira</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>1900-901</t>
+          <t>2565-913</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Torres Vedras                                                                                                                                                                                                                                                  </t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>43.5</v>
+        <v>39.1927041</v>
       </c>
       <c r="F38" t="n">
+        <v>-9.263221700000001</v>
+      </c>
+      <c r="G38" t="n">
+        <v>181.8</v>
+      </c>
+      <c r="H38" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="I38" t="n">
         <v>2</v>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1994,36 +2734,61 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cidade de Lourenço Marques</t>
+          <t>Gonçalves Zarco</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1800-867</t>
+          <t>2685-526</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>92.3</v>
+        <v>38.783051</v>
       </c>
       <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+        <v>-9.1134269</v>
+      </c>
+      <c r="G39" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="H39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2033,36 +2798,57 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>João Graça Barreto</t>
+          <t>Choupos Costa da Guia</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1950-938</t>
+          <t>2750-867</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>99.09999999999999</v>
+        <v>38.6979783</v>
       </c>
       <c r="F40" t="n">
+        <v>-9.4460683</v>
+      </c>
+      <c r="G40" t="n">
+        <v>101.1</v>
+      </c>
+      <c r="H40" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="I40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2072,36 +2858,57 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Luciano Cordeiro</t>
+          <t>General Manuel Diogo Neto</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1169-721</t>
+          <t>2765-650</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>106.3</v>
-      </c>
-      <c r="F41" t="n">
-        <v>1</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="n">
+        <v>62.5</v>
+      </c>
+      <c r="H41" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="I41" t="n">
+        <v>2</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2111,36 +2918,57 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Carlo Paggi</t>
+          <t>Combatentes do Ultramar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>1500-195</t>
+          <t>2675-683</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>123</v>
+        <v>38.7959305</v>
       </c>
       <c r="F42" t="n">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+        <v>-9.1849103</v>
+      </c>
+      <c r="G42" t="n">
+        <v>127.6</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="I42" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2150,40 +2978,57 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>António Vilar Quinta do Grafanil</t>
+          <t>Frei João Turiano</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1750-257</t>
+          <t>2675-775</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>154.2</v>
+        <v>38.7909099</v>
       </c>
       <c r="F43" t="n">
+        <v>-9.179364899999999</v>
+      </c>
+      <c r="G43" t="n">
+        <v>17.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I43" t="n">
         <v>2</v>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2193,36 +3038,57 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Jardim do Regedor</t>
+          <t>Luís</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>1150-343</t>
+          <t>2715-952</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>77.40000000000001</v>
+        <v>38.8681671</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+        <v>-9.314896299999999</v>
+      </c>
+      <c r="G44" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I44" t="n">
+        <v>1</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2232,12 +3098,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Grafanil</t>
+          <t>Portela</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1750-988</t>
+          <t>1800-336</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2246,24 +3112,45 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>170.3</v>
+        <v>38.7695153</v>
       </c>
       <c r="F45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" t="inlineStr">
+        <v>-9.1176625</v>
+      </c>
+      <c r="G45" t="n">
+        <v>187.2</v>
+      </c>
+      <c r="H45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="I45" t="n">
+        <v>2</v>
+      </c>
+      <c r="J45" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>Urgente</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -2275,40 +3162,57 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vale de Santo António</t>
+          <t>Sara Afonso Bairro Polima</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>1170-661</t>
+          <t>2785-658</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>123.5</v>
+        <v>38.7279171</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+        <v>-9.3198522</v>
+      </c>
+      <c r="G46" t="n">
+        <v>126.4</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I46" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2318,36 +3222,57 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Jorge Amado Bairro Armador</t>
+          <t>Andorinhas</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>1950-629</t>
+          <t>2565-573</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Torres Vedras                                                                                                                                                                                                                                                  </t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>22</v>
+        <v>39.1969209</v>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+        <v>-9.2341397</v>
+      </c>
+      <c r="G47" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H47" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I47" t="n">
+        <v>1</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2357,12 +3282,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>João Paulo II Bairro do Condado</t>
+          <t>Flores</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1950-461</t>
+          <t>1100-396</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2371,26 +3296,43 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>12.3</v>
+        <v>38.713555</v>
       </c>
       <c r="F48" t="n">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+        <v>-9.135401999999999</v>
+      </c>
+      <c r="G48" t="n">
+        <v>56.4</v>
+      </c>
+      <c r="H48" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="I48" t="n">
+        <v>2</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2400,12 +3342,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Rodrigues</t>
+          <t>Professor Jorge da Silva Horta</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1300-877</t>
+          <t>1500-275</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2413,23 +3355,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E49" t="n">
-        <v>26.4</v>
-      </c>
-      <c r="F49" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="n">
+        <v>44.1</v>
+      </c>
+      <c r="H49" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="I49" t="n">
+        <v>1</v>
+      </c>
+      <c r="J49" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2439,36 +3398,61 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>João Paulo II Bairro do Condado</t>
+          <t>Quinta das Pretas Quinta das Pretas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1950-874</t>
+          <t>1685-777</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>56.8</v>
+        <v>38.7929679</v>
       </c>
       <c r="F50" t="n">
-        <v>1</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+        <v>-9.2110159</v>
+      </c>
+      <c r="G50" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="I50" t="n">
+        <v>2</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2478,36 +3462,57 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Rua da Nau Catrineta</t>
+          <t>5 de Outubro Vila Verde</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>1990-407</t>
+          <t>2705-289</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>50</v>
+        <v>38.8325035</v>
       </c>
       <c r="F51" t="n">
-        <v>3</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+        <v>-9.3683771</v>
+      </c>
+      <c r="G51" t="n">
+        <v>18.2</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="I51" t="n">
+        <v>2</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2517,38 +3522,55 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Restauradores</t>
+          <t>Soudo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>1250-962</t>
+          <t>2630-319</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="F52" t="n">
+          <t xml:space="preserve">Arruda dos Vinhos                                                                                                                                                                                                                                              </t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I52" t="n">
         <v>2</v>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Urgente</t>
         </is>
       </c>
     </row>
@@ -2560,36 +3582,57 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Laje</t>
+          <t>Luís Camões</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1100-820</t>
+          <t>2630-350</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Arruda dos Vinhos                                                                                                                                                                                                                                              </t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>5.9</v>
+        <v>38.981078</v>
       </c>
       <c r="F53" t="n">
+        <v>-9.0800371</v>
+      </c>
+      <c r="G53" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I53" t="n">
         <v>2</v>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2599,36 +3642,57 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Caridade</t>
+          <t>Teixeira de Pascoais</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1150-811</t>
+          <t>2720-955</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="F54" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t xml:space="preserve">Amadora                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="I54" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2638,36 +3702,57 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Silva Freire</t>
+          <t>Memória</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>1800-972</t>
+          <t>2675-696</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>132.5</v>
+        <v>38.7903893</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+        <v>-9.1806477</v>
+      </c>
+      <c r="G55" t="n">
+        <v>190.4</v>
+      </c>
+      <c r="H55" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I55" t="n">
+        <v>3</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2677,12 +3762,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Isabéis</t>
+          <t>Coronel Bento Roma</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1200-922</t>
+          <t>1749-312</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2691,26 +3776,43 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>170.8</v>
+        <v>38.7483312</v>
       </c>
       <c r="F56" t="n">
-        <v>3</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+        <v>-9.1381032</v>
+      </c>
+      <c r="G56" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I56" t="n">
+        <v>1</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2720,36 +3822,61 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Francisco Metrass</t>
+          <t>Pinhal Verde Piçarras</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1350-783</t>
+          <t>1685-424</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Odivelas                                                                                                                                                                                                                                                       </t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>78.59999999999999</v>
+        <v>38.8200247</v>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+        <v>-9.2292685</v>
+      </c>
+      <c r="G57" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="I57" t="n">
+        <v>1</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2759,40 +3886,57 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Fontes Pereira de Melo</t>
+          <t>Bairro Novo Carapinheira</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>1050-747</t>
+          <t>2640-592</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>34.2</v>
+        <v>38.9371598</v>
       </c>
       <c r="F58" t="n">
+        <v>-9.3104441</v>
+      </c>
+      <c r="G58" t="n">
+        <v>102.1</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2802,36 +3946,57 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>António Vilar Quinta do Grafanil</t>
+          <t>Paiol</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1750-131</t>
+          <t>2580-520</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>198.1</v>
-      </c>
-      <c r="F59" t="n">
+          <t xml:space="preserve">Alenquer                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="n">
+        <v>79.40000000000001</v>
+      </c>
+      <c r="H59" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="I59" t="n">
         <v>1</v>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2841,36 +4006,57 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Esperança do Cardal</t>
+          <t>Queijadeiras</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>1150-548</t>
+          <t>2725-300</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>176.4</v>
+        <v>38.7887122</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
-      </c>
-      <c r="G60" t="inlineStr">
+        <v>-9.345323799999999</v>
+      </c>
+      <c r="G60" t="n">
+        <v>160.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I60" t="n">
+        <v>3</v>
+      </c>
+      <c r="J60" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
         <is>
           <t>Urgente</t>
         </is>
@@ -2884,12 +4070,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cidade da Beira</t>
+          <t>Sodré</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>1800-639</t>
+          <t>1249-186</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2898,26 +4084,43 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>187.6</v>
+        <v>38.7066011</v>
       </c>
       <c r="F61" t="n">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+        <v>-9.143523500000001</v>
+      </c>
+      <c r="G61" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I61" t="n">
+        <v>2</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2927,12 +4130,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Luís Oliveira Guimarães</t>
+          <t>Fiandeiras</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>1750-681</t>
+          <t>1300-198</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2941,22 +4144,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>43.9</v>
+        <v>38.7086136</v>
       </c>
       <c r="F62" t="n">
-        <v>3</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+        <v>-9.1940311</v>
+      </c>
+      <c r="G62" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="I62" t="n">
+        <v>2</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2966,12 +4190,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>São João Bosco</t>
+          <t>Conceição à Lapa</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>1350-492</t>
+          <t>1200-520</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2979,23 +4203,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E63" t="n">
-        <v>59.9</v>
-      </c>
-      <c r="F63" t="n">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="H63" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2</v>
+      </c>
+      <c r="J63" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
         <is>
           <t>Fragil</t>
         </is>
@@ -3009,40 +4250,53 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Humberto da Cruz</t>
+          <t>São Francisco Xavier Bairro Alegre</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>1900-648</t>
+          <t>2735-479</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>191.7</v>
-      </c>
-      <c r="F64" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" t="inlineStr">
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="H64" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="I64" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3052,38 +4306,55 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Fábrica de Tecidos Oriental</t>
+          <t>Ginjal Ginjal</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>1900-295</t>
+          <t>2715-676</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="F65" t="n">
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="I65" t="n">
         <v>1</v>
       </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Urgente</t>
         </is>
       </c>
     </row>
@@ -3095,36 +4366,61 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Calhariz de Benfica</t>
+          <t>Calouste Gulbenkian</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>1500-403</t>
+          <t>2770-469</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>31.2</v>
+        <v>38.7005199</v>
       </c>
       <c r="F66" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+        <v>-9.2840933</v>
+      </c>
+      <c r="G66" t="n">
+        <v>96.59999999999999</v>
+      </c>
+      <c r="H66" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="I66" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -3134,12 +4430,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Vicente Borga</t>
+          <t>Joaquim Bonifácio</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>1200-263</t>
+          <t>1169-479</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3148,24 +4444,45 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>153.8</v>
+        <v>38.7276116</v>
       </c>
       <c r="F67" t="n">
-        <v>3</v>
-      </c>
-      <c r="G67" t="inlineStr">
+        <v>-9.140586900000001</v>
+      </c>
+      <c r="G67" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="I67" t="n">
+        <v>2</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>Urgente</t>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -3177,40 +4494,57 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Barão Sabrosa</t>
+          <t>551</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>1900-927</t>
+          <t>2640-656</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100.6</v>
+        <v>38.9740199</v>
       </c>
       <c r="F68" t="n">
-        <v>1</v>
-      </c>
-      <c r="G68" t="inlineStr">
+        <v>-9.327385899999999</v>
+      </c>
+      <c r="G68" t="n">
+        <v>160.9</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I68" t="n">
+        <v>2</v>
+      </c>
+      <c r="J68" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3220,12 +4554,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>António Enes</t>
+          <t>Avenida Fontes Pereira de Melo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1069-645</t>
+          <t>1069-572</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -3234,22 +4568,43 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>168.3</v>
+        <v>41.403312</v>
       </c>
       <c r="F69" t="n">
-        <v>1</v>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+        <v>-8.535641</v>
+      </c>
+      <c r="G69" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="H69" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I69" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3259,40 +4614,57 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Merca-Tudo</t>
+          <t>Pinhal</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1200-397</t>
+          <t>2765-708</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>169.6</v>
+        <v>38.6981151</v>
       </c>
       <c r="F70" t="n">
+        <v>-9.3652845</v>
+      </c>
+      <c r="G70" t="n">
+        <v>95</v>
+      </c>
+      <c r="H70" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="I70" t="n">
         <v>2</v>
       </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -3302,12 +4674,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6 Bairro Quinta do Jacinto</t>
+          <t>Professor Mira Fernandes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1300-983</t>
+          <t>1900-648</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3316,22 +4688,47 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>56.8</v>
+        <v>38.738502</v>
       </c>
       <c r="F71" t="n">
+        <v>-9.122631200000001</v>
+      </c>
+      <c r="G71" t="n">
+        <v>39.8</v>
+      </c>
+      <c r="H71" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I71" t="n">
         <v>1</v>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Urgente</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3341,12 +4738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cantábrico</t>
+          <t>Jau</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1990-167</t>
+          <t>1349-619</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3354,23 +4751,40 @@
           <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
-      <c r="E72" t="n">
-        <v>73.40000000000001</v>
-      </c>
-      <c r="F72" t="n">
-        <v>3</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="I72" t="n">
+        <v>2</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
         <is>
           <t>Fragil</t>
         </is>
@@ -3384,12 +4798,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Cegos</t>
+          <t>Vitorino Nemésio</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1100-112</t>
+          <t>1750-949</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3398,22 +4812,43 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>158.1</v>
+        <v>38.7813203</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
-      </c>
-      <c r="G73" t="inlineStr">
+        <v>-9.1601851</v>
+      </c>
+      <c r="G73" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="H73" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="I73" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3423,36 +4858,57 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Sanches Coelho</t>
+          <t>Ribeira de Barcarena Urbanização Cabanas Golf</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>1600-180</t>
+          <t>2730-613</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>82.7</v>
+        <v>38.7330247</v>
       </c>
       <c r="F74" t="n">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+        <v>-9.2803442</v>
+      </c>
+      <c r="G74" t="n">
+        <v>156.6</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="I74" t="n">
+        <v>2</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3462,36 +4918,57 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Manuel da Fonseca Park Orange</t>
+          <t>Sacadura Cabral</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>1600-548</t>
+          <t>1495-758</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>92</v>
+        <v>38.7004318</v>
       </c>
       <c r="F75" t="n">
-        <v>1</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+        <v>-9.2457118</v>
+      </c>
+      <c r="G75" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="I75" t="n">
+        <v>2</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3501,38 +4978,59 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Palmira</t>
+          <t>Francisco do Rego</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>1170-584</t>
+          <t>2560-111</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Torres Vedras                                                                                                                                                                                                                                                  </t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>44.6</v>
+        <v>39.099983</v>
       </c>
       <c r="F76" t="n">
-        <v>2</v>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>Fragil</t>
+        <v>-9.2482088</v>
+      </c>
+      <c r="G76" t="n">
+        <v>96.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="I76" t="n">
+        <v>1</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Urgente</t>
         </is>
       </c>
     </row>
@@ -3544,12 +5042,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Nuno Krus Abecassis Alta de Lisboa</t>
+          <t>Cecílio de Sousa</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>1750-134</t>
+          <t>1200-412</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3558,22 +5056,43 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>54.2</v>
+        <v>38.7159269</v>
       </c>
       <c r="F77" t="n">
+        <v>-9.150140800000001</v>
+      </c>
+      <c r="G77" t="n">
+        <v>149.2</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="I77" t="n">
         <v>1</v>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3583,36 +5102,53 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Contrabandistas</t>
+          <t>Pomar</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>1350-302</t>
+          <t>2530-275</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E78" t="n">
-        <v>86.09999999999999</v>
-      </c>
-      <c r="F78" t="n">
-        <v>3</v>
-      </c>
-      <c r="G78" t="inlineStr">
+          <t xml:space="preserve">Lourinhã                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="n">
+        <v>120.1</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="I78" t="n">
+        <v>2</v>
+      </c>
+      <c r="J78" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3622,38 +5158,59 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Barbadinhos</t>
+          <t>Madre Deus</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>1170-452</t>
+          <t>2710-938</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>98.59999999999999</v>
+        <v>38.8161141</v>
       </c>
       <c r="F79" t="n">
-        <v>1</v>
-      </c>
-      <c r="G79" t="inlineStr">
+        <v>-9.406124200000001</v>
+      </c>
+      <c r="G79" t="n">
+        <v>164</v>
+      </c>
+      <c r="H79" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="I79" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -3665,36 +5222,61 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>República</t>
+          <t>Casal Sequeiro</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>1050-377</t>
+          <t>2665-144</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>136.2</v>
+        <v>38.9010803</v>
       </c>
       <c r="F80" t="n">
-        <v>3</v>
-      </c>
-      <c r="G80" t="inlineStr">
+        <v>-9.252296100000001</v>
+      </c>
+      <c r="G80" t="n">
+        <v>143.1</v>
+      </c>
+      <c r="H80" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I80" t="n">
+        <v>2</v>
+      </c>
+      <c r="J80" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3704,38 +5286,59 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Casal do Simão</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>1000-753</t>
+          <t>2550-342</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Cadaval                                                                                                                                                                                                                                                        </t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>182.7</v>
+        <v>39.2909903</v>
       </c>
       <c r="F81" t="n">
+        <v>-9.059528200000001</v>
+      </c>
+      <c r="G81" t="n">
+        <v>158.4</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="I81" t="n">
         <v>1</v>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="J81" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -3747,40 +5350,57 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Infante Dom Henrique</t>
+          <t>João Andrade Corvo Bairro Coopalme</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1900-773</t>
+          <t>2725-550</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>57.1</v>
+        <v>38.8013653</v>
       </c>
       <c r="F82" t="n">
+        <v>-9.352260599999999</v>
+      </c>
+      <c r="G82" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="H82" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="I82" t="n">
         <v>2</v>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="J82" t="inlineStr">
         <is>
           <t>08:00</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3790,38 +5410,59 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Luz</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>1600-930</t>
+          <t>2670-627</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>60.3</v>
+        <v>40.1147188</v>
       </c>
       <c r="F83" t="n">
-        <v>1</v>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+        <v>-8.2440038</v>
+      </c>
+      <c r="G83" t="n">
+        <v>113.2</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="I83" t="n">
+        <v>3</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -3833,40 +5474,53 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Professor Gama Pinto</t>
+          <t>I</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>1600-983</t>
+          <t>2715-101</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>84.2</v>
-      </c>
-      <c r="F84" t="n">
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="n">
+        <v>198.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="I84" t="n">
         <v>2</v>
       </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3876,12 +5530,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>João Fernandes Labrador</t>
+          <t>Manuel da Maia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>1400-267</t>
+          <t>1000-354</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3890,22 +5544,47 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>144</v>
+        <v>38.7374941</v>
       </c>
       <c r="F85" t="n">
-        <v>2</v>
-      </c>
-      <c r="G85" t="inlineStr">
+        <v>-9.1366014</v>
+      </c>
+      <c r="G85" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="H85" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="I85" t="n">
+        <v>1</v>
+      </c>
+      <c r="J85" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3915,36 +5594,57 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Almirante Reis</t>
+          <t>Eira</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>1169-616</t>
+          <t>1495-479</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>174.5</v>
+        <v>38.7059095</v>
       </c>
       <c r="F86" t="n">
-        <v>2</v>
-      </c>
-      <c r="G86" t="inlineStr">
+        <v>-9.2323383</v>
+      </c>
+      <c r="G86" t="n">
+        <v>109</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I86" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3954,40 +5654,53 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Madres</t>
+          <t>Ildefonso</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>1200-214</t>
+          <t>2050-130</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>26</v>
-      </c>
-      <c r="F87" t="n">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
+          <t xml:space="preserve">Azambuja                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3997,36 +5710,57 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Mahatma Gandhi</t>
+          <t>Dom Pedro V</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1600-545</t>
+          <t>2795-629</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>109.4</v>
+        <v>38.7100244</v>
       </c>
       <c r="F88" t="n">
-        <v>3</v>
-      </c>
-      <c r="G88" t="inlineStr">
+        <v>-9.2453314</v>
+      </c>
+      <c r="G88" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="H88" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="I88" t="n">
+        <v>1</v>
+      </c>
+      <c r="J88" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4036,40 +5770,53 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Professor Pais da Silva</t>
+          <t>249-4</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>1600-518</t>
+          <t>2785-304</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>91</v>
-      </c>
-      <c r="F89" t="n">
-        <v>1</v>
-      </c>
-      <c r="G89" t="inlineStr">
+          <t xml:space="preserve">Cascais                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="n">
+        <v>166.5</v>
+      </c>
+      <c r="H89" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="I89" t="n">
+        <v>2</v>
+      </c>
+      <c r="J89" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>Urgente</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4079,12 +5826,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Roma</t>
+          <t>Adelino Amaro da Costa</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>1700-519</t>
+          <t>1100-119</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4093,24 +5840,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>34.3</v>
+        <v>38.7117522</v>
       </c>
       <c r="F90" t="n">
-        <v>1</v>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>Urgente</t>
+        <v>-9.135682600000001</v>
+      </c>
+      <c r="G90" t="n">
+        <v>194.1</v>
+      </c>
+      <c r="H90" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="I90" t="n">
+        <v>2</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -4122,38 +5890,55 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Gonçalves Lobato</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>1300-665</t>
+          <t>2720-490</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E91" t="n">
-        <v>158.5</v>
-      </c>
-      <c r="F91" t="n">
-        <v>2</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>Urgente</t>
+          <t xml:space="preserve">Amadora                                                                                                                                                                                                                                                        </t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="H91" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="I91" t="n">
+        <v>1</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Fragil</t>
         </is>
       </c>
     </row>
@@ -4165,36 +5950,61 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Carriche</t>
+          <t>Elias Garcia</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>1750-922</t>
+          <t>2730-309</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Oeiras                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>121.3</v>
+        <v>38.7287954</v>
       </c>
       <c r="F92" t="n">
+        <v>-9.274806399999999</v>
+      </c>
+      <c r="G92" t="n">
+        <v>125.4</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="I92" t="n">
         <v>2</v>
       </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Fragil</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4204,36 +6014,57 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Veloso Salgado</t>
+          <t>Avelar Brotero</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>1600-610</t>
+          <t>2670-290</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Loures                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>101.4</v>
+        <v>38.8320284</v>
       </c>
       <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
+        <v>-9.1762418</v>
+      </c>
+      <c r="G93" t="n">
+        <v>181.9</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="I93" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
         <is>
           <t>Urgente</t>
         </is>
@@ -4247,12 +6078,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Cidade de Porto Amélia</t>
+          <t>São Francisco Borja</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>1800-808</t>
+          <t>1200-349</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4261,26 +6092,43 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>30</v>
+        <v>38.7059108</v>
       </c>
       <c r="F94" t="n">
+        <v>-9.162753800000001</v>
+      </c>
+      <c r="G94" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="H94" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="I94" t="n">
         <v>2</v>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="J94" t="inlineStr">
         <is>
           <t>10:00</t>
         </is>
       </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -4290,36 +6138,57 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>João Palma Ferreira Bairro da Flamenga</t>
+          <t>Pocinho Murgeira</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>1950-940</t>
+          <t>2640-743</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Mafra                                                                                                                                                                                                                                                          </t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>170.4</v>
+        <v>38.9576722</v>
       </c>
       <c r="F95" t="n">
-        <v>3</v>
-      </c>
-      <c r="G95" t="inlineStr">
+        <v>-9.3176463</v>
+      </c>
+      <c r="G95" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="H95" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="I95" t="n">
+        <v>1</v>
+      </c>
+      <c r="J95" t="inlineStr">
         <is>
           <t>09:00</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -4329,38 +6198,59 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Feliciano de Sousa</t>
+          <t>Norte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>1300-480</t>
+          <t>2715-806</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>52.6</v>
+        <v>38.8453431</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
+        <v>-9.317195399999999</v>
+      </c>
+      <c r="G96" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="H96" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="I96" t="n">
+        <v>3</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Urgente</t>
         </is>
       </c>
     </row>
@@ -4372,40 +6262,53 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Fragatas</t>
+          <t>São Pedro</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>1990-650</t>
+          <t>2530-570</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E97" t="n">
-        <v>170.4</v>
-      </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>Fragil</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Lourinhã                                                                                                                                                                                                                                                       </t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="n">
+        <v>46</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="I97" t="n">
+        <v>2</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -4415,12 +6318,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Costa do Castelo</t>
+          <t>Sequeiro</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>1100-554</t>
+          <t>1200-797</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -4429,22 +6332,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>147.5</v>
+        <v>38.7102558</v>
       </c>
       <c r="F98" t="n">
+        <v>-9.146032099999999</v>
+      </c>
+      <c r="G98" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="H98" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="I98" t="n">
         <v>2</v>
       </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -4454,12 +6378,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Rio Cávado</t>
+          <t>Professor Mário Chicó</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>1600-188</t>
+          <t>1600-318</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4468,26 +6392,43 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>78.3</v>
+        <v>38.7618681</v>
       </c>
       <c r="F99" t="n">
-        <v>2</v>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>Confirmar chegada</t>
-        </is>
-      </c>
+        <v>-9.1686414</v>
+      </c>
+      <c r="G99" t="n">
+        <v>182.2</v>
+      </c>
+      <c r="H99" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I99" t="n">
+        <v>3</v>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4497,12 +6438,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>José Luís Garcia Rodrigues Bairro Alto da Ajuda</t>
+          <t>Afonso Gonçalves Baldaya</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>1300-842</t>
+          <t>1400-423</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4511,22 +6452,43 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>57.4</v>
+        <v>38.6995744</v>
       </c>
       <c r="F100" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+        <v>-9.2209938</v>
+      </c>
+      <c r="G100" t="n">
+        <v>102.7</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I100" t="n">
+        <v>2</v>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
+      <c r="P100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4536,36 +6498,53 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Domingos Tendeiro</t>
+          <t>Dom João de Castro</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>1400-603</t>
+          <t>2710-281</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lisboa                                                                                                                                                                                                                                                         </t>
-        </is>
-      </c>
-      <c r="E101" t="n">
-        <v>81.40000000000001</v>
-      </c>
-      <c r="F101" t="n">
+          <t xml:space="preserve">Sintra                                                                                                                                                                                                                                                         </t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="n">
+        <v>112.9</v>
+      </c>
+      <c r="H101" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I101" t="n">
         <v>2</v>
       </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>08:00</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
+      <c r="P101" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
